--- a/tools/importer/reports/import-home-page.report.xlsx
+++ b/tools/importer/reports/import-home-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>global/en.report.json</t>
   </si>
   <si>
-    <t>["carousel-banner","carousel-category","accordion-featured","carousel-news","form"]</t>
+    <t>["carousel-banner","carousel-category","accordion-featured","carousel-news"]</t>
   </si>
   <si>
     <t>global/en</t>
@@ -52,7 +52,7 @@
     <t>home-page</t>
   </si>
   <si>
-    <t>2026-08-13T04:55:14.569Z</t>
+    <t>2026-08-13T06:57:59.756Z</t>
   </si>
   <si>
     <t>World Leading Dairy Ingredients &amp; Solutions | NZMP.com</t>
